--- a/results/helpfulness_metrics.xlsx
+++ b/results/helpfulness_metrics.xlsx
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9200994832294682</v>
+        <v>0.899384017546368</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9363174999812909</v>
+        <v>0.9168464121649528</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.9997324116091939</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14099227991515</v>
+        <v>0.1495238791557725</v>
       </c>
       <c r="F2" t="n">
         <v>0.3800385983501099</v>
@@ -512,172 +512,172 @@
         <v>0.5271034240722656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06368250001870912</v>
+        <v>0.08288599944424113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>toymix_dti_esmc_v2</t>
+          <t>toymix_dti_v2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8830040237953564</v>
+        <v>0.7971131938528411</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8948314790334224</v>
+        <v>0.8098304722176689</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9545522026148319</v>
+        <v>0.7957377210477019</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1337045556306889</v>
+        <v>0.1422331560663936</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5777354258547025</v>
+        <v>0.5802912831781497</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>bioavailability_ma</t>
+          <t>ames</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.5613568425178528</v>
+        <v>0.6611827611923218</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05972072358140945</v>
+        <v>0.014092751169967</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>toymix_dti_v2</t>
+          <t>toymix_dti_esmc_v2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8074986047071664</v>
+        <v>0.740970609116242</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8161657044387525</v>
+        <v>0.7715741592182915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8198820122951684</v>
+        <v>0.7834389219436352</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1185619849289579</v>
+        <v>0.2002684509960998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6477928073591437</v>
+        <v>0.3150849607465929</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>bioavailability_ma</t>
+          <t>cyp2c9_substrate_carbonmangels</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.5734951496124268</v>
+        <v>0.3304876685142517</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003716307856415968</v>
+        <v>0.01186476272534365</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>toymix_lpm24</t>
+          <t>toymix_dti_filtered</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7989466795704303</v>
+        <v>0.7274835697546463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8082650905213479</v>
+        <v>0.7603668588820681</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7977750385419634</v>
+        <v>0.8301402164837499</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1201346566034267</v>
+        <v>0.2003647755126259</v>
       </c>
       <c r="F5" t="n">
-        <v>0.600182355039352</v>
+        <v>0.2775930522046358</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>hia_hou</t>
+          <t>cyp2c9_substrate_carbonmangels</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7699589133262634</v>
+        <v>0.3240975737571716</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01049005197938446</v>
+        <v>0.0697733576016818</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>toymix_dti_filtered</t>
+          <t>largemix_dti</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7440373612183724</v>
+        <v>0.6727831179808346</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7795118873108519</v>
+        <v>0.697976750482587</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8781460111863297</v>
+        <v>0.7046916404525816</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2083908689648036</v>
+        <v>0.1820805014582611</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2767092653984651</v>
+        <v>0.4059504069683441</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>cyp2c9_substrate_carbonmangels</t>
+          <t>bioavailability_ma</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.3240975737571716</v>
+        <v>0.5315929651260376</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09863412387547787</v>
+        <v>0.006714889969994586</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>largemix_dti</t>
+          <t>toymix_lpm24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6904990821534139</v>
+        <v>0.6677871331189379</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7190514428040266</v>
+        <v>0.731735195569422</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7565385834947109</v>
+        <v>0.7445926687721638</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1945700616879951</v>
+        <v>0.2142491562556094</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4059504069683441</v>
+        <v>0.06673743668903977</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>bioavailability_ma</t>
+          <t>cyp2c9_substrate_carbonmangels</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.5315929651260376</v>
+        <v>0.2881594896316528</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03748714069068437</v>
+        <v>0.01285747320274178</v>
       </c>
     </row>
     <row r="8">
@@ -687,30 +687,30 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6567997959079119</v>
+        <v>0.627006819828006</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6962510600238052</v>
+        <v>0.6748376388966817</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7206990432072746</v>
+        <v>0.6834195956961133</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2223898773569773</v>
+        <v>0.2339631852230491</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3020752066317371</v>
+        <v>0.2338855993586588</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>cyp2c9_substrate_carbonmangels</t>
+          <t>cyp3a4_substrate_carbonmangels</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.3284347355365753</v>
+        <v>0.5224358439445496</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02444798318346941</v>
+        <v>0.008581956799431634</v>
       </c>
     </row>
     <row r="9">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5302468150029975</v>
+        <v>0.4975106901926197</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6765946502236541</v>
+        <v>0.6528232314389212</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7504721325464474</v>
+        <v>0.7155221127118185</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2655484231283871</v>
+        <v>0.2833972157747739</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0.4612570405006408</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07387748232279334</v>
+        <v>0.06269888127289736</v>
       </c>
     </row>
     <row r="10">
@@ -753,16 +753,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5126168732846802</v>
+        <v>0.4953094421983456</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6401963903623069</v>
+        <v>0.6159558176957022</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6785204814374717</v>
+        <v>0.5946999692827621</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2584053736954496</v>
+        <v>0.2498725608398991</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
         <v>-0.1069308742880821</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03832409107516477</v>
+        <v>0.02125584841294004</v>
       </c>
     </row>
     <row r="11">
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4918463938153668</v>
+        <v>0.4667039137418452</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5053401471564247</v>
+        <v>0.4777716631637399</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5089672909215832</v>
+        <v>0.4689141805877333</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1160675233604026</v>
+        <v>0.1020194710718052</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2948690664184642</v>
+        <v>0.2958108541467256</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>0.3272026032209396</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003627143765158491</v>
+        <v>0.008857482576006603</v>
       </c>
     </row>
     <row r="12">
@@ -819,96 +819,96 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.398136886627115</v>
+        <v>0.339579237341407</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5998590967902206</v>
+        <v>0.5811176805692356</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6856485857851105</v>
+        <v>0.6852596542601176</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3248308473909201</v>
+        <v>0.3376012688115997</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>half_life_obach</t>
+          <t>cyp3a4_substrate_carbonmangels</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-0.1428038626909256</v>
+        <v>0.4788232445716858</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08578948899488981</v>
+        <v>0.104141973690882</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Scratch</t>
+          <t>toymix</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1877401670081057</v>
+        <v>0.3343418763847187</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4509913986925931</v>
+        <v>0.4822730371343976</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4563136901674113</v>
+        <v>0.4723654861831392</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3825508685989807</v>
+        <v>0.3033139420399072</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.02301455984599771</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>cyp2c9_substrate_carbonmangels</t>
+          <t>bbb_martins</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.2767848074436188</v>
+        <v>0.5080195963382721</v>
       </c>
       <c r="I13" t="n">
-        <v>0.005322291474818219</v>
+        <v>0.009907550951258337</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>toymix</t>
+          <t>Scratch</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1748092091239874</v>
+        <v>0.1803139287056981</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4212268852962495</v>
+        <v>0.4292740875993228</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4026230245418541</v>
+        <v>0.409355930385695</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3662689505124582</v>
+        <v>0.3713182371859871</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>bbb_martins</t>
+          <t>cyp2c9_substrate_carbonmangels</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.3987668752670288</v>
+        <v>0.2767848074436188</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01860386075439541</v>
+        <v>0.01991815721362783</v>
       </c>
     </row>
     <row r="15">
@@ -918,16 +918,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1541911957573815</v>
+        <v>0.1263532751281311</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3797517009900384</v>
+        <v>0.3481922977312243</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2571623644339418</v>
+        <v>0.2087892134681532</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3509997559019469</v>
+        <v>0.3527382824923068</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0.4987654089927673</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1225893365560966</v>
+        <v>0.1394030842630711</v>
       </c>
     </row>
     <row r="16">
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04223969571187735</v>
+        <v>0.02983473612252177</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1022865599800205</v>
+        <v>0.06842079721302795</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03555784410367661</v>
+        <v>0.001366145808050276</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1262230172228891</v>
+        <v>0.102579719616269</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -974,7 +974,7 @@
         <v>5.326344966888428</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06672871587634385</v>
+        <v>0.06705465140497767</v>
       </c>
     </row>
   </sheetData>
@@ -988,7 +988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3397843480083309</v>
+        <v>0.3381394254508051</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6462418675546441</v>
+        <v>0.6417931815603838</v>
       </c>
       <c r="E2" t="n">
         <v>0.8604901430345642</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4525062207240632</v>
+        <v>0.741435520854426</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7030770275327511</v>
+        <v>0.7566972724385606</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8122689873808107</v>
+        <v>0.8101728129271535</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8652528384806796</v>
+        <v>0.8631614219842099</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8794740062004047</v>
+        <v>0.8771621424760955</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9320223261966777</v>
+        <v>0.9261937517518264</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3720723810439264</v>
+        <v>0.3589444862397879</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5330612502762918</v>
+        <v>0.5077592701951971</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7418576067488124</v>
+        <v>0.6668626361944029</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02823598427762491</v>
+        <v>0.01</v>
       </c>
       <c r="D18" t="n">
-        <v>0.07503908667754337</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9382123952713581</v>
+        <v>0.9378406992239898</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9419514743564826</v>
+        <v>0.9416244213033974</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.8667740061491266</v>
+        <v>0.8554906091682868</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8727387539732409</v>
+        <v>0.8613988278604311</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8859381670785972</v>
+        <v>0.8528011697276856</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.3055797334825867</v>
+        <v>0.236507744326113</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4438798619006323</v>
+        <v>0.3810501258034028</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3515692173841353</v>
+        <v>0.1631885068918041</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.670803644306226</v>
+        <v>0.6383935367052936</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6926118876334035</v>
+        <v>0.6613813891033803</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6794971527155272</v>
+        <v>0.5863853577407478</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1567554781292629</v>
+        <v>0.2305432523292622</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4498934744509308</v>
+        <v>0.5122787266082511</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4098395277499566</v>
+        <v>0.5556803099358962</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1634,13 +1634,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.862737777201523</v>
+        <v>0.8350795449015181</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8676801304484293</v>
+        <v>0.8440405701032526</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8574036841239244</v>
+        <v>0.8563850427576518</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.5221652037318902</v>
+        <v>0.4801918627332364</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5231015396193824</v>
+        <v>0.4810233997475135</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5058428063354703</v>
+        <v>0.4959084094534178</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9196063946315223</v>
+        <v>0.8942079539676038</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9255464246994576</v>
+        <v>0.9045532467623082</v>
       </c>
       <c r="E26" t="n">
-        <v>0.995197103272438</v>
+        <v>0.9951834515449548</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9314760841898414</v>
+        <v>0.9222478460840798</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9322899601567602</v>
+        <v>0.9233456383277807</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9113106309621625</v>
+        <v>0.8971429588725522</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.8636871520163167</v>
+        <v>0.8497540080531897</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8682855591582198</v>
+        <v>0.8546912625241179</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8559194396702152</v>
+        <v>0.8147080461712646</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.7207217070531776</v>
+        <v>0.8070179098473704</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7207217070531775</v>
+        <v>0.8200803810631588</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7207217070531775</v>
+        <v>0.8357534775103662</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.820489413782574</v>
+        <v>0.8065653912666905</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8321016803769888</v>
+        <v>0.8178853323318015</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8558739764309554</v>
+        <v>0.8140027953453788</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8405882979546798</v>
+        <v>0.8094257075313928</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8469434615722404</v>
+        <v>0.8207151232889961</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8225148134505185</v>
+        <v>0.8215376219258415</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.08996661257240476</v>
+        <v>0.0813093017109804</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2139548489088786</v>
+        <v>0.1695557998083566</v>
       </c>
       <c r="E32" t="n">
-        <v>0.08784210802617945</v>
+        <v>0.08602728891768847</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.03582460666837239</v>
+        <v>0.02862187359695395</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08342063477708771</v>
+        <v>0.03750779288515491</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03555784410367661</v>
+        <v>0.03375629017825318</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9452656437350182</v>
+        <v>0.8932757370234689</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9513120515521393</v>
+        <v>0.902338682985064</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0.9780599513508323</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
@@ -1931,16 +1931,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.6469749161323474</v>
+        <v>0.6119305061573014</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6694552416608123</v>
+        <v>0.6217775537596859</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6293472649737961</v>
+        <v>0.6285866982751573</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>6</v>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.06111060464981141</v>
+        <v>0.05699649216757818</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2909461663423052</v>
+        <v>0.2476268285167053</v>
       </c>
       <c r="E36" t="n">
         <v>0.04178436767315706</v>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.5285646203844329</v>
+        <v>0.4973711198119604</v>
       </c>
       <c r="D37" t="n">
-        <v>0.590046722129444</v>
+        <v>0.5421099200006365</v>
       </c>
       <c r="E37" t="n">
         <v>0.591850814477899</v>
@@ -2012,16 +2012,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1095556353083374</v>
+        <v>0.2252156663575262</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3232072490881517</v>
+        <v>0.3149671317024685</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2467556986981162</v>
+        <v>0.3044664024151298</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>6</v>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.3740222582710524</v>
+        <v>0.3152054858929247</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4661017343619056</v>
+        <v>0.4188621267378163</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4964231140686258</v>
+        <v>0.4277988168816809</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.4446165406883504</v>
+        <v>0.41191725299735</v>
       </c>
       <c r="D40" t="n">
-        <v>0.468321336085803</v>
+        <v>0.4207493663396981</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3925292458940503</v>
+        <v>0.3913682575521357</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2089,20 +2089,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>toymix_dti_filtered</t>
+          <t>toymix_dti_esmc_v2</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.5898890638752549</v>
+        <v>0.6001655072926717</v>
       </c>
       <c r="D41" t="n">
-        <v>0.632512536888069</v>
+        <v>0.6396698673454037</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6406817438256118</v>
+        <v>0.6313575669902226</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>6</v>
@@ -2116,17 +2116,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>toymix_rxrx3</t>
+          <t>toymix_dti_filtered</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.4457608339314862</v>
+        <v>0.5567720912566863</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4908089018972952</v>
+        <v>0.5846233757122985</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4822399789365098</v>
+        <v>0.6406817438256118</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2143,20 +2143,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>toymix_rxrx3_dti</t>
+          <t>toymix_dti_v2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.561652169575911</v>
+        <v>0.7838773124828881</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5957064486626452</v>
+        <v>0.8010683723195019</v>
       </c>
       <c r="E43" t="n">
-        <v>0.555756818134336</v>
+        <v>0.8096539717108342</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>6</v>
@@ -2165,82 +2165,82 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Excretion</t>
+          <t>Metabolism</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Scratch</t>
+          <t>toymix_lpm24</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.07391965500765212</v>
+        <v>0.4590073315809851</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1942651220538696</v>
+        <v>0.588722913046232</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08113087031559224</v>
+        <v>0.6028947473947126</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Excretion</t>
+          <t>Metabolism</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dti</t>
+          <t>toymix_rxrx3</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.1706684190573934</v>
+        <v>0.2549908246751023</v>
       </c>
       <c r="D45" t="n">
-        <v>0.195454516898721</v>
+        <v>0.4433642365497841</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2022038385851385</v>
+        <v>0.4820567842769324</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Excretion</t>
+          <t>Metabolism</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>largemix</t>
+          <t>toymix_rxrx3_dti</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0.4910890464109056</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0.544201622314646</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0.5548414733087579</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -2251,17 +2251,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>largemix_dti</t>
+          <t>Scratch</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.5821711681691637</v>
+        <v>0.07310445915533277</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6028298431858472</v>
+        <v>0.1888351520747279</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5820796803515456</v>
+        <v>0.08113087031559224</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>rxrx3</t>
+          <t>dti</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.1464817156360921</v>
+        <v>0.1687862648817133</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2193461104034883</v>
+        <v>0.1921493930697658</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2696029328405549</v>
+        <v>0.2022038385851385</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2305,20 +2305,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>rxrx3_dti</t>
+          <t>largemix</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.1050370013176596</v>
+        <v>0.9889718661128094</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2653781547837243</v>
+        <v>0.9890930387702621</v>
       </c>
       <c r="E49" t="n">
-        <v>0.191735954027711</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>3</v>
@@ -2332,17 +2332,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>toymix</t>
+          <t>largemix_dti</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.1843213835312266</v>
+        <v>0.575750906581332</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2514887141905045</v>
+        <v>0.594042405229805</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1388887256927238</v>
+        <v>0.5820796803515456</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2359,17 +2359,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>toymix_bbbc047</t>
+          <t>rxrx3</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.6985398406519213</v>
+        <v>0.1448662956640318</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7082863858689811</v>
+        <v>0.2154669792341574</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7676324604809355</v>
+        <v>0.2696029328405549</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2386,17 +2386,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>toymix_dti</t>
+          <t>rxrx3_dti</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.4950768413596431</v>
+        <v>0.1038786392040194</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5056661879528443</v>
+        <v>0.258786003664315</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4395164183386047</v>
+        <v>0.191735954027711</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2413,17 +2413,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>toymix_dti_filtered</t>
+          <t>toymix</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.6213321792564608</v>
+        <v>0.1897727762624275</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6442496938797851</v>
+        <v>0.3274598957570389</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5389625302778782</v>
+        <v>0.1491943064027961</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2440,17 +2440,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>toymix_rxrx3</t>
+          <t>toymix_bbbc047</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.02227603846668598</v>
+        <v>0.6908362497636751</v>
       </c>
       <c r="D54" t="n">
-        <v>0.03684619301503978</v>
+        <v>0.6994846860941283</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.7676324604809355</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2467,17 +2467,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>toymix_rxrx3_dti</t>
+          <t>toymix_dti</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.4522058610167569</v>
+        <v>0.4896170676686815</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4542187129312392</v>
+        <v>0.4984924151482438</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4538088174443819</v>
+        <v>0.4395164183386047</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2489,163 +2489,163 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Toxicity</t>
+          <t>Excretion</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Scratch</t>
+          <t>toymix_dti_esmc_v2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.2799606340466668</v>
+        <v>0.6031848540072388</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6446628388663571</v>
+        <v>0.612451298122539</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7893256777327142</v>
+        <v>0.5474804965906677</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Toxicity</t>
+          <t>Excretion</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>dti</t>
+          <t>toymix_dti_filtered</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.0530841542617143</v>
+        <v>0.6144800447952007</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1432766944964535</v>
+        <v>0.6344508524853106</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1172685490013716</v>
+        <v>0.5389625302778782</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Toxicity</t>
+          <t>Excretion</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>largemix</t>
+          <t>toymix_dti_v2</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.955861941447268</v>
+        <v>0.7991848652794451</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9582418911854593</v>
+        <v>0.8099298145617815</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9941093777652675</v>
+        <v>0.7401519555890399</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Toxicity</t>
+          <t>Excretion</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>largemix_dti</t>
+          <t>toymix_lpm24</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.7457169400497908</v>
+        <v>0.5715724366082717</v>
       </c>
       <c r="D59" t="n">
-        <v>0.7572607792826394</v>
+        <v>0.5824332742255556</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7186233778060858</v>
+        <v>0.6447690192660015</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Toxicity</t>
+          <t>Excretion</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>rxrx3</t>
+          <t>toymix_rxrx3</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.402407359394828</v>
+        <v>0.02227603846668598</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5094491212663499</v>
+        <v>0.03684619301503978</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4541871749083222</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Toxicity</t>
+          <t>Excretion</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>rxrx3_dti</t>
+          <t>toymix_rxrx3_dti</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.7288782989310006</v>
+        <v>0.4472188742368918</v>
       </c>
       <c r="D61" t="n">
-        <v>0.7550302901709629</v>
+        <v>0.4486921334680377</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8007473537978016</v>
+        <v>0.4538088174443819</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -2656,20 +2656,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>toymix</t>
+          <t>Scratch</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.08822993188482489</v>
+        <v>0.2723194046515252</v>
       </c>
       <c r="D62" t="n">
-        <v>0.2512848127169413</v>
+        <v>0.6215381930407211</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1449838406103827</v>
+        <v>0.7430763860814422</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>4</v>
@@ -2683,17 +2683,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>toymix_bbbc047</t>
+          <t>dti</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.7208030500896268</v>
+        <v>0.02412192794040575</v>
       </c>
       <c r="D63" t="n">
-        <v>0.7321177616612414</v>
+        <v>0.0846424199957677</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6667395066510241</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -2710,20 +2710,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>toymix_dti</t>
+          <t>largemix</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.5192177378432586</v>
+        <v>0.9259677742809129</v>
       </c>
       <c r="D64" t="n">
-        <v>0.5343967870516979</v>
+        <v>0.9330364717583295</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5677707178886184</v>
+        <v>0.9941093777652675</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G64" t="n">
         <v>4</v>
@@ -2737,17 +2737,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>toymix_dti_filtered</t>
+          <t>largemix_dti</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.7402012549984448</v>
+        <v>0.7155630820569361</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7698087158246341</v>
+        <v>0.7279620264180504</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8318468698290309</v>
+        <v>0.6600258720769079</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>toymix_rxrx3</t>
+          <t>rxrx3</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.8090932546368129</v>
+        <v>0.1826157058527739</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8244312314046564</v>
+        <v>0.4508830605311924</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8745700192421642</v>
+        <v>0.422724352904559</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -2791,22 +2791,265 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>rxrx3_dti</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.6918054184404222</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.7219793309349221</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.7346454353257201</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Toxicity</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>toymix</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.3700850496304924</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.4152011312536757</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.3729623456959672</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Toxicity</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>toymix_bbbc047</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.6780806126427082</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.6965653148713665</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.6529820748570476</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Toxicity</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>toymix_dti</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.4684741133750598</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.4910670142184405</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.4846391944001565</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Toxicity</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>toymix_dti_esmc_v2</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.8193021643664888</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.8306564523047195</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.8712440958579095</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Toxicity</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>toymix_dti_filtered</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.7246039359908024</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.750402173647569</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.795933795275072</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Toxicity</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>toymix_dti_v2</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.8021042700878961</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.8188405652849733</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.8475354889808717</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Toxicity</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>toymix_lpm24</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.8508436140146728</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.8552904829468723</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.8668102240274522</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Toxicity</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>toymix_rxrx3</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.7896553455403532</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.8031827012443958</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.8320729589216435</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Toxicity</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>toymix_rxrx3_dti</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>0.7306578467952518</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0.7895154500588155</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.9037362157030193</v>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
+      <c r="C76" t="n">
+        <v>0.7181374156667797</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.7728150616914692</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.8876409379382726</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2926,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
         <v>7</v>
@@ -2935,16 +3178,16 @@
         <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>8</v>
@@ -2978,7 +3221,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -3030,7 +3273,7 @@
         <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
         <v>19</v>
@@ -3039,16 +3282,16 @@
         <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
         <v>18</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
         <v>20</v>
@@ -3082,7 +3325,7 @@
         <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
@@ -3091,16 +3334,16 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
         <v>14</v>
@@ -3134,7 +3377,7 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
@@ -3143,16 +3386,16 @@
         <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>5</v>
@@ -3186,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
         <v>7</v>
@@ -3195,16 +3438,16 @@
         <v>17</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
@@ -3220,22 +3463,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -3244,10 +3487,10 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -3256,10 +3499,10 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
         <v>5</v>
@@ -3299,16 +3542,16 @@
         <v>17</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
         <v>12</v>
@@ -3342,7 +3585,7 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -3360,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
@@ -3376,49 +3619,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -3455,16 +3698,16 @@
         <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
         <v>12</v>
@@ -3480,49 +3723,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21</v>
+      </c>
+      <c r="G13" t="n">
+        <v>18</v>
+      </c>
+      <c r="H13" t="n">
+        <v>19</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22</v>
+      </c>
+      <c r="K13" t="n">
         <v>9</v>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>9</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -3532,49 +3775,49 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>18</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22</v>
+      </c>
+      <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="C14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3602,7 +3845,7 @@
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
@@ -3611,16 +3854,16 @@
         <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3663,16 +3906,16 @@
         <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>9</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>13</v>
@@ -3734,19 +3977,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1593427197419083</v>
+        <v>0.2035909650749936</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1587592090561989</v>
+        <v>0.1078285049171746</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01293095788411827</v>
+        <v>0.1316973776296604</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4496066981034894</v>
+        <v>0.4368691776193234</v>
       </c>
     </row>
     <row r="3">
@@ -3756,19 +3999,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1502979563646358</v>
+        <v>0.1292024973723644</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2119742375202246</v>
+        <v>0.2097640958068886</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1455004712962283</v>
+        <v>-0.1504791925831764</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3584256775272987</v>
+        <v>0.3689561670702145</v>
       </c>
     </row>
     <row r="4">
@@ -3778,19 +4021,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.159418952793262</v>
+        <v>0.11389942867495</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1709355835443422</v>
+        <v>0.1807729701862065</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03354897125072423</v>
+        <v>-0.05396065357756705</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4703771775728028</v>
+        <v>0.4654747060758239</v>
       </c>
     </row>
   </sheetData>
@@ -3932,64 +4175,64 @@
         <v>0.4019184762342503</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2952380952380952</v>
+        <v>0.2761904761904762</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.07655590023509529</v>
+        <v>-0.05741692517632146</v>
       </c>
       <c r="F2" t="n">
         <v>0.7142857142857143</v>
       </c>
       <c r="G2" t="n">
+        <v>0.4095238095238096</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6380952380952382</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5428571428571429</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6380952380952382</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6380952380952382</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6380952380952382</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.5428571428571429</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1913897505877382</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.3904761904761905</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.6923076923076924</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6263736263736264</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.6969696969696969</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.7272727272727272</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.606060606060606</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0909090909090909</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.5151515151515151</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.4242424242424242</v>
-      </c>
       <c r="R2" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="S2" t="n">
-        <v>0.442760992000533</v>
+        <v>0.4976133515281193</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="V2" t="n">
-        <v>0.606060606060606</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3523809523809524</v>
       </c>
     </row>
     <row r="3">
@@ -4005,64 +4248,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2679456508228335</v>
+        <v>0.2870846258816073</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3653846153846154</v>
+        <v>0.3461538461538462</v>
       </c>
       <c r="F3" t="n">
         <v>0.4976133515281194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2488066757640597</v>
+        <v>0.2296677007052859</v>
       </c>
       <c r="H3" t="n">
+        <v>0.3636405261167026</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4976133515281194</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5933082268219885</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.3445015510579288</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.5303948353054367</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.5524946201098299</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.2595495470347952</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3511552695176641</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5343667144834019</v>
+        <v>0.535891301645667</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04580286124143444</v>
+        <v>0.07655590023509529</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5343667144834019</v>
+        <v>0.535891301645667</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07633810206905742</v>
+        <v>0.1634615384615385</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5343667144834019</v>
+        <v>0.5550302767044407</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3816905103452871</v>
+        <v>0.421057451293024</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5076923076923078</v>
+        <v>0.4807692307692308</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.04580286124143444</v>
+        <v>-0.09569487529386911</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1679438245519263</v>
+        <v>0.2679456508228335</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1679438245519263</v>
+        <v>0.2296677007052859</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2900847878624181</v>
+        <v>0.2679456508228335</v>
       </c>
     </row>
     <row r="4">
@@ -4072,10 +4315,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2952380952380952</v>
+        <v>0.2761904761904762</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2679456508228335</v>
+        <v>0.2870846258816073</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -4084,58 +4327,58 @@
         <v>0.05741692517632146</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2571428571428572</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4857142857142858</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="H4" t="n">
         <v>0.3904761904761905</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3626373626373627</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.4095238095238096</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1212121212121212</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1619047619047619</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.1238095238095238</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0763381020690574</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.1047619047619048</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6363636363636362</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="W4" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3142857142857143</v>
       </c>
     </row>
     <row r="5">
@@ -4145,10 +4388,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.07655590023509529</v>
+        <v>-0.05741692517632146</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3653846153846154</v>
+        <v>0.3461538461538462</v>
       </c>
       <c r="D5" t="n">
         <v>0.05741692517632146</v>
@@ -4157,58 +4400,58 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1339728254114168</v>
+        <v>0.1531118004701906</v>
       </c>
       <c r="G5" t="n">
         <v>0.03827795011754764</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01913897505877382</v>
+        <v>0.05741692517632146</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1988980632395388</v>
+        <v>0.2296677007052859</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08839913921757278</v>
+        <v>0.210528725646512</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01526762041381148</v>
+        <v>0.03827795011754764</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1374085837243033</v>
+        <v>0.1913897505877382</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1984790653795493</v>
+        <v>0.1148338503526429</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1984790653795493</v>
+        <v>0.03827795011754764</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2595495470347952</v>
+        <v>0.2296677007052859</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1068733428966804</v>
+        <v>0.2788461538461539</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07633810206905742</v>
+        <v>0.1722507755289644</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01526762041381148</v>
+        <v>0.03827795011754764</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04615384615384616</v>
+        <v>0.0576923076923077</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2595495470347952</v>
+        <v>-0.210528725646512</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2595495470347952</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1679438245519263</v>
+        <v>-0.07655590023509529</v>
       </c>
       <c r="W5" t="n">
-        <v>0.442760992000533</v>
+        <v>0.3445015510579288</v>
       </c>
     </row>
     <row r="6">
@@ -4224,64 +4467,64 @@
         <v>0.4976133515281194</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2571428571428572</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1339728254114168</v>
+        <v>0.1531118004701906</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
+        <v>0.2761904761904762</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.561904761904762</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5428571428571429</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5047619047619049</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.580952380952381</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.2571428571428572</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.5428571428571429</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.8241758241758242</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.4945054945054945</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.2727272727272727</v>
-      </c>
       <c r="O6" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2870846258816073</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5649019553110248</v>
+        <v>0.5167523265868932</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3333333333333334</v>
       </c>
     </row>
     <row r="7">
@@ -4291,70 +4534,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3904761904761905</v>
+        <v>0.4095238095238096</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2488066757640597</v>
+        <v>0.2296677007052859</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4857142857142858</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="E7" t="n">
         <v>0.03827795011754764</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2571428571428572</v>
+        <v>0.2761904761904762</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4857142857142858</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3626373626373627</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4725274725274726</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6363636363636362</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.01913897505877382</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0303030303030303</v>
+        <v>0.06666666666666668</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1068733428966804</v>
+        <v>0.1339728254114168</v>
       </c>
       <c r="T7" t="n">
-        <v>0.606060606060606</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3714285714285714</v>
       </c>
     </row>
     <row r="8">
@@ -4364,70 +4607,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3445015510579288</v>
+        <v>0.3636405261167026</v>
       </c>
       <c r="D8" t="n">
         <v>0.3904761904761905</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01913897505877382</v>
+        <v>0.05741692517632146</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5428571428571429</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4857142857142858</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5604395604395604</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6969696969696969</v>
+        <v>0.6380952380952382</v>
       </c>
       <c r="L8" t="n">
-        <v>0.606060606060606</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3062236009403811</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3816905103452871</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="U8" t="n">
-        <v>0.606060606060606</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="V8" t="n">
-        <v>0.606060606060606</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="9">
@@ -4437,70 +4680,70 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6923076923076924</v>
+        <v>0.6380952380952382</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5303948353054367</v>
+        <v>0.4976133515281194</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1988980632395388</v>
+        <v>0.2296677007052859</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8241758241758242</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3626373626373627</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5604395604395604</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5824175824175825</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6363636363636362</v>
+        <v>0.580952380952381</v>
       </c>
       <c r="N9" t="n">
-        <v>0.303030303030303</v>
+        <v>0.180952380952381</v>
       </c>
       <c r="O9" t="n">
-        <v>0.606060606060606</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.325362575999155</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4732962328281559</v>
+        <v>0.4401964263517978</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5047619047619049</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4857142857142858</v>
       </c>
     </row>
     <row r="10">
@@ -4510,70 +4753,70 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6263736263736264</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5524946201098299</v>
+        <v>0.5933082268219885</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3626373626373627</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08839913921757278</v>
+        <v>0.210528725646512</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4945054945054945</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4725274725274726</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5824175824175825</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0909090909090909</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.1913897505877382</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3904761904761905</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5038314736557788</v>
+        <v>0.4593354014105717</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="V10" t="n">
-        <v>0.606060606060606</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="11">
@@ -4583,70 +4826,70 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6969696969696969</v>
+        <v>0.6380952380952382</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2595495470347952</v>
+        <v>0.3445015510579288</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01526762041381148</v>
+        <v>0.03827795011754764</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6969696969696969</v>
+        <v>0.6380952380952382</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.6952380952380953</v>
       </c>
       <c r="M11" t="n">
-        <v>0.606060606060606</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2488066757640597</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.303030303030303</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3206200286900411</v>
+        <v>0.4401964263517978</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5047619047619049</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4095238095238096</v>
       </c>
     </row>
     <row r="12">
@@ -4656,70 +4899,70 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.6380952380952382</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3511552695176641</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1374085837243033</v>
+        <v>0.1913897505877382</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5047619047619049</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6363636363636362</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="H12" t="n">
-        <v>0.606060606060606</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.6952380952380953</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7575757575757575</v>
+        <v>0.6952380952380953</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.180952380952381</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2488066757640597</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3511552695176641</v>
+        <v>0.4019184762342503</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -4729,70 +4972,70 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.606060606060606</v>
+        <v>0.6380952380952382</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5343667144834019</v>
+        <v>0.535891301645667</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.4095238095238096</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1984790653795493</v>
+        <v>0.1148338503526429</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.580952380952381</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6363636363636362</v>
+        <v>0.580952380952381</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="K13" t="n">
-        <v>0.606060606060606</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7575757575757575</v>
+        <v>0.6952380952380953</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1339728254114168</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4095238095238096</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4732962328281559</v>
+        <v>0.4784743764693455</v>
       </c>
       <c r="T13" t="n">
-        <v>0.303030303030303</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.5047619047619049</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="14">
@@ -4802,70 +5045,70 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04580286124143444</v>
+        <v>0.07655590023509529</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1984790653795493</v>
+        <v>0.03827795011754764</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2571428571428572</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="I14" t="n">
-        <v>0.303030303030303</v>
+        <v>0.180952380952381</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0909090909090909</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.180952380952381</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2761904761904762</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.1148338503526429</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.2761904761904762</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="S14" t="n">
-        <v>0.04580286124143445</v>
+        <v>0.09569487529386911</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0303030303030303</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1212121212121212</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1212121212121212</v>
+        <v>-0.1238095238095238</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3142857142857143</v>
       </c>
     </row>
     <row r="15">
@@ -4875,70 +5118,70 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5343667144834019</v>
+        <v>0.535891301645667</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2595495470347952</v>
+        <v>0.2296677007052859</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="I15" t="n">
-        <v>0.606060606060606</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2761904761904762</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4732962328281559</v>
+        <v>0.4401964263517978</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="V15" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.5428571428571429</v>
       </c>
     </row>
     <row r="16">
@@ -4948,70 +5191,70 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.1913897505877382</v>
       </c>
       <c r="C16" t="n">
-        <v>0.07633810206905742</v>
+        <v>0.1634615384615385</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1212121212121212</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1068733428966804</v>
+        <v>0.2788461538461539</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2870846258816073</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.01913897505877382</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3062236009403811</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.325362575999155</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.1913897505877382</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2488066757640597</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2488066757640597</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1339728254114168</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.1148338503526429</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.4593354014105717</v>
       </c>
       <c r="R16" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3816905103452871</v>
+        <v>0.4903846153846154</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.03827795011754764</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.325362575999155</v>
       </c>
       <c r="V16" t="n">
-        <v>0.303030303030303</v>
+        <v>0.325362575999155</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2296677007052859</v>
       </c>
     </row>
     <row r="17">
@@ -5021,70 +5264,70 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.3904761904761905</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5343667144834019</v>
+        <v>0.5550302767044407</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1619047619047619</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07633810206905742</v>
+        <v>0.1722507755289644</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="K17" t="n">
-        <v>0.303030303030303</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.2761904761904762</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.4593354014105717</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7175781594491396</v>
+        <v>0.5741692517632146</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1212121212121212</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1619047619047619</v>
       </c>
     </row>
     <row r="18">
@@ -5094,70 +5337,70 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3816905103452871</v>
+        <v>0.421057451293024</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.1238095238095238</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01526762041381148</v>
+        <v>0.03827795011754764</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0303030303030303</v>
+        <v>0.06666666666666668</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3904761904761905</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4095238095238096</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="P18" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5649019553110248</v>
+        <v>0.6315861769395361</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.1619047619047619</v>
       </c>
     </row>
     <row r="19">
@@ -5167,70 +5410,70 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.442760992000533</v>
+        <v>0.4976133515281193</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5076923076923078</v>
+        <v>0.4807692307692308</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0763381020690574</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04615384615384616</v>
+        <v>0.0576923076923077</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5649019553110248</v>
+        <v>0.5167523265868932</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1068733428966804</v>
+        <v>0.1339728254114168</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3816905103452871</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4732962328281559</v>
+        <v>0.4401964263517978</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5038314736557788</v>
+        <v>0.4593354014105717</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3206200286900411</v>
+        <v>0.4401964263517978</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3511552695176641</v>
+        <v>0.4019184762342503</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4732962328281559</v>
+        <v>0.4784743764693455</v>
       </c>
       <c r="N19" t="n">
-        <v>0.04580286124143445</v>
+        <v>0.09569487529386911</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4732962328281559</v>
+        <v>0.4401964263517978</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3816905103452871</v>
+        <v>0.4903846153846154</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7175781594491396</v>
+        <v>0.5741692517632146</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5649019553110248</v>
+        <v>0.6315861769395361</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1984790653795493</v>
+        <v>0.1148338503526429</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1679438245519263</v>
+        <v>0.2870846258816073</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2900847878624181</v>
+        <v>0.4401964263517978</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1679438245519263</v>
+        <v>0.210528725646512</v>
       </c>
     </row>
     <row r="20">
@@ -5240,70 +5483,70 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.04580286124143444</v>
+        <v>-0.09569487529386911</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2595495470347952</v>
+        <v>-0.210528725646512</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="G20" t="n">
-        <v>0.606060606060606</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="M20" t="n">
-        <v>0.303030303030303</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0303030303030303</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.03827795011754764</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1212121212121212</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1984790653795493</v>
+        <v>0.1148338503526429</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="W20" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.08571428571428572</v>
       </c>
     </row>
     <row r="21">
@@ -5313,70 +5556,70 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1679438245519263</v>
+        <v>0.2679456508228335</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.1047619047619048</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2595495470347952</v>
+        <v>0.3827795011754764</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="H21" t="n">
-        <v>0.606060606060606</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1212121212121212</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.325362575999155</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1679438245519263</v>
+        <v>0.2870846258816073</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2952380952380952</v>
       </c>
     </row>
     <row r="22">
@@ -5386,70 +5629,70 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.606060606060606</v>
+        <v>0.561904761904762</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1679438245519263</v>
+        <v>0.2296677007052859</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6363636363636362</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1679438245519263</v>
+        <v>-0.07655590023509529</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="H22" t="n">
-        <v>0.606060606060606</v>
+        <v>0.4476190476190477</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5047619047619049</v>
       </c>
       <c r="J22" t="n">
-        <v>0.606060606060606</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5047619047619049</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.5047619047619049</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1212121212121212</v>
+        <v>-0.1238095238095238</v>
       </c>
       <c r="O22" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="P22" t="n">
-        <v>0.303030303030303</v>
+        <v>0.325362575999155</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2900847878624181</v>
+        <v>0.4401964263517978</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.219047619047619</v>
       </c>
     </row>
     <row r="23">
@@ -5459,70 +5702,70 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2900847878624181</v>
+        <v>0.2679456508228335</v>
       </c>
       <c r="D23" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="E23" t="n">
-        <v>0.442760992000533</v>
+        <v>0.3445015510579288</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.4857142857142858</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4095238095238096</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4242424242424242</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2296677007052859</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1619047619047619</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.1619047619047619</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1679438245519263</v>
+        <v>0.210528725646512</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="W23" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5628,7 +5871,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9301299915198087</v>
+        <v>0.9034378755542464</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -5646,7 +5889,7 @@
         <v>0.9512896810152875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0210006970699442</v>
+        <v>0.4724557231868952</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -5655,7 +5898,7 @@
         <v>0.512091775507696</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9990812730836867</v>
+        <v>0.9986888113422397</v>
       </c>
       <c r="L2" t="n">
         <v>0.9834852283959511</v>
@@ -5698,7 +5941,7 @@
         <v>0.5045535995069661</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7404371772115298</v>
+        <v>0.8410746943336971</v>
       </c>
       <c r="I3" t="n">
         <v>0.9212203541149132</v>
@@ -5707,7 +5950,7 @@
         <v>0.4134791030411503</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9908925371622261</v>
+        <v>0.9890709654475194</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -5750,7 +5993,7 @@
         <v>0.8460971835957732</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8374648732997489</v>
+        <v>0.8591190200483642</v>
       </c>
       <c r="I4" t="n">
         <v>0.781392927483447</v>
@@ -5759,7 +6002,7 @@
         <v>0.5727091519116382</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9545522026148319</v>
+        <v>0.9428950537251293</v>
       </c>
       <c r="L4" t="n">
         <v>0.8021984910117216</v>
@@ -5802,7 +6045,7 @@
         <v>0.6775438101594161</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9596932772820157</v>
+        <v>0.7792709315206099</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5906,7 +6149,7 @@
         <v>0.8000697507758671</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7870731014618723</v>
+        <v>0.7154702266704011</v>
       </c>
       <c r="I7" t="n">
         <v>0.8165373595848701</v>
@@ -5940,49 +6183,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7418576067488124</v>
+        <v>0.6668626361944029</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2251172600326301</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8859381670785972</v>
+        <v>0.8528011697276856</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3515692173841353</v>
+        <v>0.1631885068918041</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6794971527155272</v>
+        <v>0.5863853577407478</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.02301455984599771</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7593950181567983</v>
+        <v>0.6894949784875406</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5675534030692591</v>
+        <v>0.4419199517220487</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7814421708259345</v>
+        <v>0.7184762887419697</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9113106309621625</v>
+        <v>0.8855447870195532</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8559194396702152</v>
+        <v>0.8147080461712646</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7207217070531775</v>
+        <v>0.6365881665308792</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8558739764309554</v>
+        <v>0.8140027953453788</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7325196164599194</v>
+        <v>0.654811793134863</v>
       </c>
     </row>
     <row r="9">
@@ -6010,7 +6253,7 @@
         <v>0.9103969640271982</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9398408956028357</v>
+        <v>0.9581413100428594</v>
       </c>
       <c r="I9" t="n">
         <v>0.9862416890645652</v>
@@ -6019,15 +6262,17 @@
         <v>0.4959084094534178</v>
       </c>
       <c r="K9" t="n">
-        <v>0.995197103272438</v>
+        <v>0.9951834515449548</v>
       </c>
       <c r="L9" t="n">
         <v>0.9873491690912368</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9838766195194876</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>0.9838925326490823</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9878994991482309</v>
+      </c>
       <c r="O9" t="n">
         <v>0.9856936204096826</v>
       </c>
@@ -6042,47 +6287,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7667750331252136</v>
+        <v>0.7658640634363388</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.825854423069448</v>
+        <v>0.8248732639101922</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7430482366349657</v>
+        <v>0.7421654556474478</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09132400859493303</v>
+        <v>0.09121551079557533</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4879415461574852</v>
+        <v>0.4873618455421946</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4098395277499566</v>
+        <v>0.5556803099358962</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8574036841239244</v>
+        <v>0.8563850427576518</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5058428063354703</v>
+        <v>0.5052418380670737</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8982100804168812</v>
+        <v>0.8971429588725522</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7650606182849568</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>0.7654732087520069</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8357534775103662</v>
+      </c>
       <c r="O10" t="n">
-        <v>0.6547374442903289</v>
+        <v>0.653959581240343</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8225148134505185</v>
+        <v>0.8215376219258415</v>
       </c>
     </row>
     <row r="11">
@@ -6092,43 +6339,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05950549878154994</v>
+        <v>0.05587586056456798</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04364717536324329</v>
+        <v>0.03995633532460072</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6058511867475402</v>
+        <v>0.6043300533502627</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003844450179138966</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5109736309623847</v>
+        <v>0.5090863378459749</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.1415648353957906</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5635081338232597</v>
+        <v>0.5618235864316224</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3983405032266013</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>0.396018526542772</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.527949822708489</v>
+      </c>
       <c r="L11" t="n">
-        <v>0.4966135727326895</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>0.4946708600300078</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.624235997739061</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5276712343868096</v>
+      </c>
       <c r="O11" t="n">
-        <v>0.6198480255568966</v>
+        <v>0.6183809099778984</v>
       </c>
       <c r="P11" t="n">
-        <v>0.525640450253621</v>
+        <v>0.5238097606024649</v>
       </c>
     </row>
     <row r="12">
@@ -6156,7 +6409,7 @@
         <v>0.5806870481310217</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3954065213337515</v>
+        <v>0.4673679694344691</v>
       </c>
       <c r="I12" t="n">
         <v>0.6821533020505185</v>
@@ -6164,12 +6417,18 @@
       <c r="J12" t="n">
         <v>0.3867179885614994</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0.7513178792130881</v>
+      </c>
       <c r="L12" t="n">
         <v>0.6456119763660463</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0.6852186667460036</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.7321393124121177</v>
+      </c>
       <c r="O12" t="n">
         <v>0.7355803895346125</v>
       </c>
@@ -6202,7 +6461,7 @@
         <v>0.6030145808247763</v>
       </c>
       <c r="H13" t="n">
-        <v>0.445732097132678</v>
+        <v>0.4722752491793833</v>
       </c>
       <c r="I13" t="n">
         <v>0.7415492469360964</v>
@@ -6210,12 +6469,18 @@
       <c r="J13" t="n">
         <v>0.3811826424147253</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0.7347653112719562</v>
+      </c>
       <c r="L13" t="n">
         <v>0.6357515112851774</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0.6082933485066812</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5755865646656476</v>
+      </c>
       <c r="O13" t="n">
         <v>0.7165597272798921</v>
       </c>
@@ -6233,40 +6498,46 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02746851284410993</v>
+        <v>0.02755624503190564</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7281460139509101</v>
+        <v>0.7304716528816081</v>
       </c>
       <c r="E14" t="n">
-        <v>0.455351857855492</v>
+        <v>0.4568062145195468</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9051332866211397</v>
+        <v>0.9080242084534451</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1774259838320031</v>
+        <v>0.1779926679412495</v>
       </c>
       <c r="H14" t="n">
+        <v>0.6480409841311253</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.07303767061129984</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2958108541467256</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.3150849607465929</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2775930522046358</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.07280513694690496</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.2948690664184642</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>0.2767092653984651</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>0.06673743668903977</v>
+      </c>
       <c r="O14" t="n">
-        <v>0.344631932316123</v>
+        <v>0.3457326585759665</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3020752066317371</v>
+        <v>0.3030400101836093</v>
       </c>
     </row>
     <row r="15">
@@ -6276,43 +6547,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02778768663668641</v>
+        <v>0.02656836024337296</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04598533761022815</v>
+        <v>0.04396749652159454</v>
       </c>
       <c r="D15" t="n">
+        <v>0.9561199027016647</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7476146284721746</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.707845723727459</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.08013613871737096</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2937740473317393</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5558649562401707</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.7819255998747373</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.7403315439071306</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.0981048760624809</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.3072564921006615</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.5813757821267901</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0.7690112902675568</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+        <v>0.735267000027098</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.9340892766756648</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6302029301237775</v>
+      </c>
       <c r="O15" t="n">
-        <v>0.2551267191918805</v>
+        <v>0.2439317339303357</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9514734555811466</v>
+        <v>0.9097227077734625</v>
       </c>
     </row>
     <row r="16">
@@ -6322,43 +6599,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6654742480108675</v>
+        <v>0.4039289180180307</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3834227828449449</v>
+        <v>0.1135666804328286</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9797262953619251</v>
+        <v>0.7274405423271121</v>
       </c>
       <c r="E16" t="n">
+        <v>0.7483116207290269</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4941680273004727</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6740331615333374</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.08041761335667189</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1608349070656211</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5089012301322958</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5089012301322958</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.718845854360826</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.9545729442496014</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="F16" t="n">
-        <v>0.7531305259072386</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.927847545119348</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.429338094313992</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.7674420337667379</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0.9713776052784786</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>0.2731066175043666</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5002979235396857</v>
+        <v>0.2338855993586588</v>
       </c>
     </row>
     <row r="17">
@@ -6368,43 +6651,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4978444375814634</v>
+        <v>0.4815545276440383</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3030288417954322</v>
+        <v>0.2931134703085667</v>
       </c>
       <c r="D17" t="n">
+        <v>0.9672791163107862</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7793101159634876</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3440190618165569</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5846220569652339</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.774000874134296</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7805749191662815</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6362029233338651</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7677888852509107</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8690059903279396</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.8056724298316141</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.3556564553245495</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.604398510323462</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.5306024694273325</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8069800184908399</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.6577242417476667</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>0.8984025145113631</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>0.670790013397989</v>
+      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5067020361393815</v>
+        <v>0.490122297749777</v>
       </c>
     </row>
     <row r="18">
@@ -6432,7 +6721,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1388887256927238</v>
+        <v>0.1491943064027961</v>
       </c>
       <c r="I18" t="n">
         <v>0.550246678635168</v>
@@ -6440,12 +6729,18 @@
       <c r="J18" t="n">
         <v>0.4197579037722617</v>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0.5474804965906677</v>
+      </c>
       <c r="L18" t="n">
         <v>0.5389625302778782</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0.7401519555890399</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4317407900126764</v>
+      </c>
       <c r="O18" t="n">
         <v>0.1105385790451194</v>
       </c>
@@ -6478,7 +6773,7 @@
         <v>0.191735954027711</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08497494745145737</v>
+        <v>0.05918450673402454</v>
       </c>
       <c r="I19" t="n">
         <v>0.7676324604809355</v>
@@ -6486,12 +6781,18 @@
       <c r="J19" t="n">
         <v>0.4395164183386047</v>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>0.5220845125260385</v>
+      </c>
       <c r="L19" t="n">
         <v>0.495384036850114</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0.6896374880963047</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.6447690192660015</v>
+      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
@@ -6524,7 +6825,7 @@
         <v>0.9461339797992203</v>
       </c>
       <c r="H20" t="n">
-        <v>0.032970468732541</v>
+        <v>0.4703680518951827</v>
       </c>
       <c r="I20" t="n">
         <v>0.9666331556526331</v>
@@ -6532,12 +6833,18 @@
       <c r="J20" t="n">
         <v>0.6216353276445792</v>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0.9433992330794595</v>
+      </c>
       <c r="L20" t="n">
         <v>0.9448017361765592</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0.9183035820376044</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.9583457849555277</v>
+      </c>
       <c r="O20" t="n">
         <v>0.9690442364573756</v>
       </c>
@@ -6552,43 +6859,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8827313370966056</v>
+        <v>0.7902327537940617</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2345370980027432</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8447488092113021</v>
+        <v>0.7439271315027831</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7700289303544563</v>
+        <v>0.6528339188961007</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2357822749165041</v>
+        <v>0.001518031975874419</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7015359991519615</v>
+        <v>0.5693321622077987</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.2755566394967517</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6558737412782374</v>
+        <v>0.5136639541187379</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5139061081326576</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>0.3405870167996279</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.7990889586363596</v>
+      </c>
       <c r="L21" t="n">
-        <v>0.9506017557769018</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+        <v>0.8729755870686412</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.9043521360204049</v>
+      </c>
       <c r="O21" t="n">
-        <v>0.9169780305018986</v>
+        <v>0.8319839098608572</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0.9331984465306147</v>
       </c>
     </row>
     <row r="22">
@@ -6616,7 +6929,7 @@
         <v>0.4724924732890278</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2569972124882244</v>
+        <v>0.2034288111551972</v>
       </c>
       <c r="I22" t="n">
         <v>0.6776052720238108</v>
@@ -6624,12 +6937,18 @@
       <c r="J22" t="n">
         <v>0.3476430611557337</v>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0.6272643973159201</v>
+      </c>
       <c r="L22" t="n">
         <v>0.4649393678635729</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0.5802912831781497</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.729195698777057</v>
+      </c>
       <c r="O22" t="n">
         <v>0.5795406506769212</v>
       </c>
@@ -6662,7 +6981,7 @@
         <v>0.8999587084436416</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7151715696469997</v>
+        <v>0.7114510224675712</v>
       </c>
       <c r="I23" t="n">
         <v>0.6283588776902843</v>
@@ -6670,12 +6989,18 @@
       <c r="J23" t="n">
         <v>0.6544026512738212</v>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0.9528732201871393</v>
+      </c>
       <c r="L23" t="n">
         <v>0.7188920034815027</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0.7767673959241391</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.8292683120344995</v>
+      </c>
       <c r="O23" t="n">
         <v>0.8321620079824297</v>
       </c>
@@ -6786,7 +7111,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8253733515739441</v>
+        <v>0.9545385837554932</v>
       </c>
       <c r="C2" t="n">
         <v>5.326344966888428</v>
@@ -6804,7 +7129,7 @@
         <v>0.7229799628257751</v>
       </c>
       <c r="H2" t="n">
-        <v>5.22472095489502</v>
+        <v>3.04009485244751</v>
       </c>
       <c r="I2" t="n">
         <v>0.4872669279575348</v>
@@ -6813,7 +7138,7 @@
         <v>2.848292902112007</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4917127192020416</v>
+        <v>0.4936118721961975</v>
       </c>
       <c r="L2" t="n">
         <v>0.5671831965446472</v>
@@ -6856,7 +7181,7 @@
         <v>0.7267488837242126</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8788065612316132</v>
       </c>
       <c r="I3" t="n">
         <v>0.9150205254554749</v>
@@ -6865,7 +7190,7 @@
         <v>0.6855967044830322</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9465020298957824</v>
+        <v>0.9456789493560792</v>
       </c>
       <c r="L3" t="n">
         <v>0.950617253780365</v>
@@ -6908,7 +7233,7 @@
         <v>0.8194481730461121</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8155491352081299</v>
+        <v>0.8253298699855804</v>
       </c>
       <c r="I4" t="n">
         <v>0.7902225852012634</v>
@@ -6917,7 +7242,7 @@
         <v>0.6959643959999084</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8684350848197937</v>
+        <v>0.86316978931427</v>
       </c>
       <c r="L4" t="n">
         <v>0.7996200323104858</v>
@@ -6960,7 +7285,7 @@
         <v>0.5786498785018921</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6275357604026794</v>
+        <v>0.5962753593921661</v>
       </c>
       <c r="I5" t="n">
         <v>0.4612570405006408</v>
@@ -7064,7 +7389,7 @@
         <v>1.464130640029907</v>
       </c>
       <c r="H7" t="n">
-        <v>1.495716452598572</v>
+        <v>1.669733226299286</v>
       </c>
       <c r="I7" t="n">
         <v>1.42410933971405</v>
@@ -7116,7 +7441,7 @@
         <v>0.7043303847312927</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3987668752670288</v>
+        <v>0.5080195963382721</v>
       </c>
       <c r="I8" t="n">
         <v>0.7402597069740295</v>
@@ -7125,16 +7450,16 @@
         <v>0.6539903283119202</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7501741051673889</v>
+        <v>0.7503584623336792</v>
       </c>
       <c r="L8" t="n">
         <v>0.8085747361183167</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7836658358573914</v>
+        <v>0.7838911414146423</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7228686809539795</v>
+        <v>0.7218239307403564</v>
       </c>
       <c r="O8" t="n">
         <v>0.7836453914642334</v>
@@ -7168,7 +7493,7 @@
         <v>15.72943210601807</v>
       </c>
       <c r="H9" t="n">
-        <v>13.37019443511963</v>
+        <v>11.90384721755981</v>
       </c>
       <c r="I9" t="n">
         <v>9.652263641357422</v>
@@ -7177,15 +7502,17 @@
         <v>48.94092798233032</v>
       </c>
       <c r="K9" t="n">
-        <v>8.934698104858398</v>
+        <v>8.935791969299316</v>
       </c>
       <c r="L9" t="n">
         <v>9.563525199890137</v>
       </c>
       <c r="M9" t="n">
-        <v>9.841768264770508</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>9.840493202209473</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.519429206848145</v>
+      </c>
       <c r="O9" t="n">
         <v>9.696178436279297</v>
       </c>
@@ -7218,7 +7545,7 @@
         <v>0.2888145744800567</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2425856739282608</v>
+        <v>0.3293006494641304</v>
       </c>
       <c r="I10" t="n">
         <v>0.5075007081031799</v>
@@ -7227,15 +7554,17 @@
         <v>0.2994104027748108</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5919040441513062</v>
+        <v>0.5926080942153931</v>
       </c>
       <c r="L10" t="n">
         <v>0.5316541790962219</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4528424739837646</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>0.4536256194114685</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4952742755413055</v>
+      </c>
       <c r="O10" t="n">
         <v>0.3875417411327362</v>
       </c>
@@ -7268,7 +7597,7 @@
         <v>0.4020613729953766</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1469020247459411</v>
+        <v>0.2192417085170746</v>
       </c>
       <c r="I11" t="n">
         <v>0.4282949566841125</v>
@@ -7276,12 +7605,18 @@
       <c r="J11" t="n">
         <v>0.3458169922232628</v>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0.4114448130130768</v>
+      </c>
       <c r="L11" t="n">
         <v>0.394890546798706</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0.4593413472175598</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.411306232213974</v>
+      </c>
       <c r="O11" t="n">
         <v>0.4564287960529327</v>
       </c>
@@ -7314,7 +7649,7 @@
         <v>0.6514849662780762</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5835561156272888</v>
+        <v>0.6099391281604767</v>
       </c>
       <c r="I12" t="n">
         <v>0.6886852383613586</v>
@@ -7322,12 +7657,18 @@
       <c r="J12" t="n">
         <v>0.5803706645965576</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0.7140428423881531</v>
+      </c>
       <c r="L12" t="n">
         <v>0.675288200378418</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0.6898090839385986</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.7070114612579346</v>
+      </c>
       <c r="O12" t="n">
         <v>0.7082730531692505</v>
       </c>
@@ -7360,7 +7701,7 @@
         <v>0.584186315536499</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5148394703865051</v>
+        <v>0.5265425145626068</v>
       </c>
       <c r="I13" t="n">
         <v>0.645267128944397</v>
@@ -7368,12 +7709,18 @@
       <c r="J13" t="n">
         <v>0.4863792061805725</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0.6422760486602783</v>
+      </c>
       <c r="L13" t="n">
         <v>0.5986202359199524</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0.5865137577056885</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.57209312915802</v>
+      </c>
       <c r="O13" t="n">
         <v>0.6342490911483765</v>
       </c>
@@ -7406,7 +7753,7 @@
         <v>0.3071217536926269</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4477684795856476</v>
+        <v>0.3872364610433578</v>
       </c>
       <c r="I14" t="n">
         <v>0.2892332971096039</v>
@@ -7414,12 +7761,18 @@
       <c r="J14" t="n">
         <v>0.3272026032209396</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0.3304876685142517</v>
+      </c>
       <c r="L14" t="n">
         <v>0.3240975737571716</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0.4472241103649139</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2881594896316528</v>
+      </c>
       <c r="O14" t="n">
         <v>0.3357112407684326</v>
       </c>
@@ -7452,7 +7805,7 @@
         <v>0.5499960780143738</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3311899304389953</v>
+        <v>0.326321005821228</v>
       </c>
       <c r="I15" t="n">
         <v>0.4024477303028106</v>
@@ -7460,12 +7813,18 @@
       <c r="J15" t="n">
         <v>0.4958399683237076</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0.6541009545326233</v>
+      </c>
       <c r="L15" t="n">
         <v>0.5597672462463379</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0.6306146383285522</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5223292112350464</v>
+      </c>
       <c r="O15" t="n">
         <v>0.3846871554851532</v>
       </c>
@@ -7498,7 +7857,7 @@
         <v>0.6045100688934326</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4263965487480163</v>
+        <v>0.4938187003135681</v>
       </c>
       <c r="I16" t="n">
         <v>0.5088140964508057</v>
@@ -7506,12 +7865,18 @@
       <c r="J16" t="n">
         <v>0.5737179517745972</v>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0.5737179517745972</v>
+      </c>
       <c r="L16" t="n">
         <v>0.6128662824630737</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0.6568222641944885</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6652930378913879</v>
+      </c>
       <c r="O16" t="n">
         <v>0.4788232445716858</v>
       </c>
@@ -7544,7 +7909,7 @@
         <v>0.142021968960762</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1072452142834663</v>
+        <v>0.2342866696417331</v>
       </c>
       <c r="I17" t="n">
         <v>0.2374895215034485</v>
@@ -7552,12 +7917,18 @@
       <c r="J17" t="n">
         <v>0.1671519875526428</v>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0.23126021027565</v>
+      </c>
       <c r="L17" t="n">
         <v>0.2805728316307068</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0.3443926572799682</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1840026974678039</v>
+      </c>
       <c r="O17" t="n">
         <v>-0.1428038626909256</v>
       </c>
@@ -7590,7 +7961,7 @@
         <v>-0.1069308742880821</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0334827490150928</v>
+        <v>-0.0280328784137964</v>
       </c>
       <c r="I18" t="n">
         <v>0.1840544939041137</v>
@@ -7598,12 +7969,18 @@
       <c r="J18" t="n">
         <v>0.1150484904646873</v>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0.1825916618108749</v>
+      </c>
       <c r="L18" t="n">
         <v>0.1780871301889419</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0.2844815552234649</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1213853657245636</v>
+      </c>
       <c r="O18" t="n">
         <v>-0.0484750755131244</v>
       </c>
@@ -7636,7 +8013,7 @@
         <v>0.0520414784550666</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0018087003845721</v>
+        <v>-0.01032611855771395</v>
       </c>
       <c r="I19" t="n">
         <v>0.3230100870132446</v>
@@ -7644,12 +8021,18 @@
       <c r="J19" t="n">
         <v>0.1686261892318726</v>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>0.2074758112430572</v>
+      </c>
       <c r="L19" t="n">
         <v>0.1949128061532974</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0.2863121926784515</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2652008533477783</v>
+      </c>
       <c r="O19" t="n">
         <v>-0.038173384964466</v>
       </c>
@@ -7682,7 +8065,7 @@
         <v>0.8444064855575562</v>
       </c>
       <c r="H20" t="n">
-        <v>2.688150882720948</v>
+        <v>1.805012941360474</v>
       </c>
       <c r="I20" t="n">
         <v>0.8030171394348145</v>
@@ -7690,12 +8073,18 @@
       <c r="J20" t="n">
         <v>1.499593168497086</v>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0.8499281406402588</v>
+      </c>
       <c r="L20" t="n">
         <v>0.8470963835716248</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0.9005981087684631</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.8197499513626099</v>
+      </c>
       <c r="O20" t="n">
         <v>0.7981489896774292</v>
       </c>
@@ -7728,7 +8117,7 @@
         <v>0.6832845211029053</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4079504907131195</v>
+        <v>0.5887096673250198</v>
       </c>
       <c r="I21" t="n">
         <v>0.6653633117675781</v>
@@ -7736,12 +8125,18 @@
       <c r="J21" t="n">
         <v>0.6096448302268982</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>0.7572498917579651</v>
+      </c>
       <c r="L21" t="n">
         <v>0.7810361385345459</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0.8219289779663086</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.791137158870697</v>
+      </c>
       <c r="O21" t="n">
         <v>0.7678397297859192</v>
       </c>
@@ -7774,7 +8169,7 @@
         <v>0.6312403678894043</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5713840126991272</v>
+        <v>0.5565047562122345</v>
       </c>
       <c r="I22" t="n">
         <v>0.6882128715515137</v>
@@ -7782,12 +8177,18 @@
       <c r="J22" t="n">
         <v>0.5965619683265686</v>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0.6742300987243652</v>
+      </c>
       <c r="L22" t="n">
         <v>0.6291424036026001</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0.6611827611923218</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.7025427222251892</v>
+      </c>
       <c r="O22" t="n">
         <v>0.6609742641448975</v>
       </c>
@@ -7820,7 +8221,7 @@
         <v>0.7952173948287964</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6980434656143188</v>
+        <v>0.6960869431495667</v>
       </c>
       <c r="I23" t="n">
         <v>0.6523913145065308</v>
@@ -7828,12 +8229,18 @@
       <c r="J23" t="n">
         <v>0.6660869419574738</v>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0.8230435252189636</v>
+      </c>
       <c r="L23" t="n">
         <v>0.6999999284744263</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0.7304348349571228</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.7580434679985046</v>
+      </c>
       <c r="O23" t="n">
         <v>0.7595651745796204</v>
       </c>
@@ -7902,44 +8309,44 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5665956066161975</v>
+        <v>0.5696345543266439</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.02938076578546645</v>
+        <v>-0.03215513058745815</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4853261012886979</v>
+        <v>0.4875723245656301</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>toymix_dti_filtered</t>
+          <t>toymix_dti_v2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4298107915868526</v>
+        <v>0.5278581148197051</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1272858747404138</v>
+        <v>-0.1202694980662746</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3285204886182588</v>
+        <v>0.3805563846183462</v>
       </c>
     </row>
     <row r="4">
@@ -7949,247 +8356,247 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3414697758044504</v>
+        <v>0.411093042888542</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1549098512915421</v>
+        <v>-0.09338874642166177</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2863164839048957</v>
+        <v>0.3423000716189687</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>largemix_dti</t>
+          <t>toymix_dti_filtered</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4002438906319514</v>
+        <v>0.4329546926212251</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08443021327661428</v>
+        <v>-0.1272858747404138</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2680600441114335</v>
+        <v>0.3310927712827452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>toymix_rxrx3_dti</t>
+          <t>toymix_lpm24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3931665104228011</v>
+        <v>0.3919165007764704</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1491586029130254</v>
+        <v>-0.1000881596585718</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2452596613312121</v>
+        <v>0.3024611079700991</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>toymix_bbbc047</t>
+          <t>largemix_dti</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3991246827030624</v>
+        <v>0.4026692564091221</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1462283866946567</v>
+        <v>-0.08854158651902343</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2256032515310609</v>
+        <v>0.2687026628832643</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>toymix_dti_v2</t>
+          <t>toymix_rxrx3_dti</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.3940580995611803</v>
+      </c>
+      <c r="D8" t="n">
         <v>6</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.3790337135210436</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.1351152991114097</v>
+        <v>-0.1504219107394982</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2076507093102258</v>
+        <v>0.2455635512973588</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rxrx3_dti</t>
+          <t>toymix_bbbc047</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3716493430323794</v>
+        <v>0.3998899288297501</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1300726232149512</v>
+        <v>-0.1543239668535838</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1892049916697137</v>
+        <v>0.2235491438395984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>toymix_rxrx3</t>
+          <t>rxrx3_dti</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3295177045754435</v>
+        <v>0.3717907040591685</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1672698132385506</v>
+        <v>-0.1372589743385018</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1488676980976275</v>
+        <v>0.1866817300963793</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>toymix_lpm24</t>
+          <t>toymix_rxrx3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3470266687986709</v>
+        <v>0.3338468444415503</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1165199512073087</v>
+        <v>-0.1666620971054526</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1483638316532511</v>
+        <v>0.1518435929699129</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>toymix_dti</t>
+          <t>toymix</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3451096195821983</v>
+        <v>0.3868252983940186</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2945642968782082</v>
+        <v>-0.3475926690956577</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05434874846383164</v>
+        <v>0.0529989495350748</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>toymix</t>
+          <t>toymix_dti</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4222590906499913</v>
+        <v>0.3430872085530421</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4817881174426786</v>
+        <v>-0.3050099840219329</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.02976451339634369</v>
+        <v>0.04849757556441711</v>
       </c>
     </row>
     <row r="14">
@@ -8202,19 +8609,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3416164252415425</v>
+        <v>0.3423006443938396</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3071574822420389</v>
+        <v>-0.3230146094463488</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.07123969770255473</v>
+        <v>-0.08108178986809852</v>
       </c>
     </row>
     <row r="15">
@@ -8227,19 +8634,19 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>0.145654906030327</v>
+        <v>0.1454772104034459</v>
       </c>
       <c r="D15" t="n">
         <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5502750717198605</v>
+        <v>-0.5680454153408179</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3487048387125727</v>
+        <v>-0.3608532903862949</v>
       </c>
     </row>
   </sheetData>
